--- a/Data/Export/Model/ModelConfig_模型配置.xlsx
+++ b/Data/Export/Model/ModelConfig_模型配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FB8014-BB10-43C2-BD34-96C4C67F7AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3235343F-0F89-400E-9489-73E3A6FF070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="2550" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelConfig" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -267,6 +267,22 @@
   </si>
   <si>
     <t>modelKind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卫城一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卫城二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卫城三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卫城四</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1462,10 +1478,21 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="B27" s="4">
+        <v>23</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1475,10 +1502,21 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="B28" s="4">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1488,10 +1526,21 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="B29" s="4">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1501,10 +1550,21 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="B30" s="4">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>

--- a/Data/Export/Model/ModelConfig_模型配置.xlsx
+++ b/Data/Export/Model/ModelConfig_模型配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3235343F-0F89-400E-9489-73E3A6FF070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CB6B15-EF2E-4ABE-99CC-A64BA1035562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelConfig" sheetId="36" r:id="rId1"/>
@@ -1485,7 +1485,7 @@
         <v>62</v>
       </c>
       <c r="D27" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -1509,7 +1509,7 @@
         <v>63</v>
       </c>
       <c r="D28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
@@ -1533,7 +1533,7 @@
         <v>64</v>
       </c>
       <c r="D29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -1557,7 +1557,7 @@
         <v>65</v>
       </c>
       <c r="D30" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
